--- a/metricasProjeto.xlsx
+++ b/metricasProjeto.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nicol\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e6e916cefa585604/Área de Trabalho/mack/charles/trab2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{91D3D7FA-615C-4693-BF80-FB6894F0F410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="121" documentId="13_ncr:9_{91D3D7FA-615C-4693-BF80-FB6894F0F410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A109208C-480C-4C0D-9787-228861F791EA}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15870" activeTab="2" xr2:uid="{5F6A9E50-989E-4DA6-9E69-DD156C9E29C5}"/>
   </bookViews>
@@ -17,12 +17,25 @@
     <sheet name="Tabela 1" sheetId="2" r:id="rId2"/>
     <sheet name="Tabela 2" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="40">
   <si>
     <t>Algoritmo</t>
   </si>
@@ -132,10 +145,16 @@
     <t>Tempo Num</t>
   </si>
   <si>
-    <t>Bubble Sort</t>
+    <t>0.488000</t>
   </si>
   <si>
-    <t>Merge Sort</t>
+    <t>0.496000</t>
+  </si>
+  <si>
+    <t>0.411000</t>
+  </si>
+  <si>
+    <t>0.397000</t>
   </si>
 </sst>
 </file>
@@ -143,9 +162,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="169" formatCode="0.0000000000"/>
+    <numFmt numFmtId="164" formatCode="0.0000000000"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -280,8 +299,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -461,8 +488,14 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor theme="4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -577,6 +610,50 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="4"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -622,24 +699,31 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Ênfase1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -687,32 +771,32 @@
   </cellStyles>
   <dxfs count="9">
     <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
+      <numFmt numFmtId="164" formatCode="0.0000000000"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
+      <numFmt numFmtId="164" formatCode="0.0000000000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0000000000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0000000000"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="169" formatCode="0.0000000000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="169" formatCode="0.0000000000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="169" formatCode="0.0000000000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="169" formatCode="0.0000000000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="169" formatCode="0.0000000000"/>
+      <numFmt numFmtId="164" formatCode="0.0000000000"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -842,10 +926,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'Tabela 1'!$A$2:$A$5</c:f>
+              <c:f>'Tabela 1'!$A$2:$A$6</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>1000</c:v>
                 </c:pt>
@@ -858,15 +942,18 @@
                 <c:pt idx="3">
                   <c:v>200000</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>500000</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Tabela 1'!$B$2:$B$5</c:f>
+              <c:f>'Tabela 1'!$B$2:$B$6</c:f>
               <c:numCache>
                 <c:formatCode>0.0000000000</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>5.6000000000000008E-3</c:v>
                 </c:pt>
@@ -878,6 +965,9 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>363.49519999999995</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2133.9906000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -929,10 +1019,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'Tabela 1'!$A$2:$A$5</c:f>
+              <c:f>'Tabela 1'!$A$2:$A$6</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>1000</c:v>
                 </c:pt>
@@ -945,15 +1035,18 @@
                 <c:pt idx="3">
                   <c:v>200000</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>500000</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Tabela 1'!$D$2:$D$5</c:f>
+              <c:f>'Tabela 1'!$D$2:$D$6</c:f>
               <c:numCache>
                 <c:formatCode>0.0000000000</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>8.0000000000000004E-4</c:v>
                 </c:pt>
@@ -965,6 +1058,9 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0.14499999999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.45600000000000007</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1040,13 +1136,13 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>'Tabela 1'!$A$2:$A$5</c15:sqref>
+                          <c15:sqref>'Tabela 1'!$A$2:$A$6</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
                     <c:numCache>
                       <c:formatCode>0</c:formatCode>
-                      <c:ptCount val="4"/>
+                      <c:ptCount val="5"/>
                       <c:pt idx="0">
                         <c:v>1000</c:v>
                       </c:pt>
@@ -1059,6 +1155,9 @@
                       <c:pt idx="3">
                         <c:v>200000</c:v>
                       </c:pt>
+                      <c:pt idx="4">
+                        <c:v>500000</c:v>
+                      </c:pt>
                     </c:numCache>
                   </c:numRef>
                 </c:cat>
@@ -1067,13 +1166,13 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>'Tabela 1'!$A$2:$A$5</c15:sqref>
+                          <c15:sqref>'Tabela 1'!$A$2:$A$6</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
                     <c:numCache>
                       <c:formatCode>0</c:formatCode>
-                      <c:ptCount val="4"/>
+                      <c:ptCount val="5"/>
                       <c:pt idx="0">
                         <c:v>1000</c:v>
                       </c:pt>
@@ -1085,6 +1184,9 @@
                       </c:pt>
                       <c:pt idx="3">
                         <c:v>200000</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>500000</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -1374,7 +1476,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Bubble Sort</c:v>
+                  <c:v>Bubble Sort - Medido (Média)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1405,10 +1507,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'Tabela 2'!$B$15:$B$18</c:f>
+              <c:f>'Tabela 2'!$B$15:$B$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>1000</c:v>
                 </c:pt>
@@ -1421,15 +1523,18 @@
                 <c:pt idx="3">
                   <c:v>200000</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>500000</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Tabela 2'!$C$15:$C$18</c:f>
+              <c:f>'Tabela 2'!$C$15:$C$19</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>499500</c:v>
                 </c:pt>
@@ -1442,13 +1547,16 @@
                 <c:pt idx="3">
                   <c:v>19999900000</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>124999750000</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-FD26-42D9-B707-35B0BBBC8430}"/>
+              <c16:uniqueId val="{00000003-A16B-4AFD-9FE3-DE9F5A9FB55F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1461,7 +1569,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Merge Sort</c:v>
+                  <c:v>Merge Sort - Medido (Média)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1492,10 +1600,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'Tabela 2'!$B$15:$B$18</c:f>
+              <c:f>'Tabela 2'!$B$15:$B$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>1000</c:v>
                 </c:pt>
@@ -1508,15 +1616,18 @@
                 <c:pt idx="3">
                   <c:v>200000</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>500000</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Tabela 2'!$D$15:$D$18</c:f>
+              <c:f>'Tabela 2'!$D$15:$D$19</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>8694.6</c:v>
                 </c:pt>
@@ -1529,13 +1640,16 @@
                 <c:pt idx="3">
                   <c:v>3264479</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>8812929</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-FD26-42D9-B707-35B0BBBC8430}"/>
+              <c16:uniqueId val="{00000004-A16B-4AFD-9FE3-DE9F5A9FB55F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1603,13 +1717,13 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>'Tabela 2'!$B$15:$B$18</c15:sqref>
+                          <c15:sqref>'Tabela 2'!$B$15:$B$19</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
                     <c:numCache>
                       <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="4"/>
+                      <c:ptCount val="5"/>
                       <c:pt idx="0">
                         <c:v>1000</c:v>
                       </c:pt>
@@ -1622,6 +1736,9 @@
                       <c:pt idx="3">
                         <c:v>200000</c:v>
                       </c:pt>
+                      <c:pt idx="4">
+                        <c:v>500000</c:v>
+                      </c:pt>
                     </c:numCache>
                   </c:numRef>
                 </c:cat>
@@ -1630,13 +1747,13 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>'Tabela 2'!$B$15:$B$18</c15:sqref>
+                          <c15:sqref>'Tabela 2'!$B$15:$B$19</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
                     <c:numCache>
                       <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="4"/>
+                      <c:ptCount val="5"/>
                       <c:pt idx="0">
                         <c:v>1000</c:v>
                       </c:pt>
@@ -1649,13 +1766,16 @@
                       <c:pt idx="3">
                         <c:v>200000</c:v>
                       </c:pt>
+                      <c:pt idx="4">
+                        <c:v>500000</c:v>
+                      </c:pt>
                     </c:numCache>
                   </c:numRef>
                 </c:val>
                 <c:smooth val="0"/>
                 <c:extLst>
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                    <c16:uniqueId val="{00000000-FD26-42D9-B707-35B0BBBC8430}"/>
+                    <c16:uniqueId val="{00000002-A16B-4AFD-9FE3-DE9F5A9FB55F}"/>
                   </c:ext>
                 </c:extLst>
               </c15:ser>
@@ -1735,7 +1855,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3054,28 +3174,28 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E9FD18D0-D139-4AF5-AE1B-51A5AB3A6D0E}" name="Tabela1" displayName="Tabela1" ref="A1:E5" totalsRowShown="0" headerRowDxfId="8" dataDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E9FD18D0-D139-4AF5-AE1B-51A5AB3A6D0E}" name="Tabela1" displayName="Tabela1" ref="A1:E6" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{BBD4EDC9-AA0D-4962-BBA4-BB7A7196DC33}" name="Alunos" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{BBD4EDC9-AA0D-4962-BBA4-BB7A7196DC33}" name="Alunos" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{89636E85-78DE-4CFE-B848-D4DB5401C6A6}" name="Bubble Sort (Média)" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{77F4655B-B4A6-4065-AF04-A3FE4A8F281A}" name="Bubble Sort (DV)" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{5EA45014-9CDE-4C12-BA22-38DB0EF3AC26}" name="Merge Sort (Média)" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{5BCF7E3A-542C-427E-9F16-3084F48EB33D}" name="Merge Sort (DV)" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{77F4655B-B4A6-4065-AF04-A3FE4A8F281A}" name="Bubble Sort (DV)" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{5EA45014-9CDE-4C12-BA22-38DB0EF3AC26}" name="Merge Sort (Média)" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{5BCF7E3A-542C-427E-9F16-3084F48EB33D}" name="Merge Sort (DV)" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{25C816C1-154A-4919-B85C-AAE7B2AD38CF}" name="Tabela4" displayName="Tabela4" ref="A1:G5" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{25C816C1-154A-4919-B85C-AAE7B2AD38CF}" name="Tabela4" displayName="Tabela4" ref="A1:G6" totalsRowShown="0">
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{21B76CBD-AB99-4B5C-AD58-960CA2C28E24}" name="Alunos"/>
-    <tableColumn id="2" xr3:uid="{D0915508-2B6B-49A2-9376-3AC191A1D029}" name="Bubble Sort - Medido (Média)" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{D0915508-2B6B-49A2-9376-3AC191A1D029}" name="Bubble Sort - Medido (Média)" dataDxfId="8"/>
     <tableColumn id="3" xr3:uid="{79C76B65-AE19-4431-9EBC-343A78309BD0}" name="Bubble Sort - Medido (DV)"/>
     <tableColumn id="4" xr3:uid="{900CED56-4FC4-4937-9FC7-A59715857CB9}" name="Bubble  Sort - Teórico O(n^2)">
       <calculatedColumnFormula>'Tabela 1'!A2^2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{02C4840F-0FA2-4196-90B2-0BE756F74147}" name="Merge Sort - Medido (Média)" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{02C4840F-0FA2-4196-90B2-0BE756F74147}" name="Merge Sort - Medido (Média)" dataDxfId="7"/>
     <tableColumn id="6" xr3:uid="{65DE7B07-7252-4376-8980-F846BE55676A}" name="Merge Sort - Medido (DV)"/>
     <tableColumn id="7" xr3:uid="{B2E02F9A-9DA5-42D8-B9B1-E04EA7DCD328}" name="Merge Sort - Teórico (O n log n)">
       <calculatedColumnFormula>'Tabela 1'!A2*(LOG('Tabela 1'!A2,2))</calculatedColumnFormula>
@@ -3402,14 +3522,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36FE1A98-114F-4354-8FD5-49AE4B739705}">
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.28515625" customWidth="1"/>
     <col min="3" max="3" width="9.140625" style="2"/>
-    <col min="4" max="4" width="14.140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="14.140625" customWidth="1"/>
     <col min="5" max="5" width="17.140625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3422,7 +3542,7 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
@@ -3442,7 +3562,7 @@
       <c r="C2" s="2">
         <v>1</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="2">
@@ -3463,14 +3583,14 @@
       <c r="C3" s="2">
         <v>2</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" t="s">
         <v>6</v>
       </c>
       <c r="E3" s="2">
         <v>499500</v>
       </c>
       <c r="F3">
-        <f t="shared" ref="F3:F41" si="0">VALUE(SUBSTITUTE(D3,".",","))</f>
+        <f t="shared" ref="F3:F46" si="0">VALUE(SUBSTITUTE(D3,".",","))</f>
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
@@ -3484,7 +3604,7 @@
       <c r="C4" s="2">
         <v>3</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" t="s">
         <v>7</v>
       </c>
       <c r="E4" s="2">
@@ -3505,7 +3625,7 @@
       <c r="C5" s="2">
         <v>4</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" t="s">
         <v>7</v>
       </c>
       <c r="E5" s="2">
@@ -3526,7 +3646,7 @@
       <c r="C6" s="2">
         <v>5</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" t="s">
         <v>6</v>
       </c>
       <c r="E6" s="2">
@@ -3547,7 +3667,7 @@
       <c r="C7" s="2">
         <v>1</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" t="s">
         <v>8</v>
       </c>
       <c r="E7" s="2">
@@ -3568,7 +3688,7 @@
       <c r="C8" s="2">
         <v>2</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" t="s">
         <v>9</v>
       </c>
       <c r="E8" s="2">
@@ -3589,7 +3709,7 @@
       <c r="C9" s="2">
         <v>3</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" t="s">
         <v>10</v>
       </c>
       <c r="E9" s="2">
@@ -3610,7 +3730,7 @@
       <c r="C10" s="2">
         <v>4</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" t="s">
         <v>11</v>
       </c>
       <c r="E10" s="2">
@@ -3631,7 +3751,7 @@
       <c r="C11" s="2">
         <v>5</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" t="s">
         <v>12</v>
       </c>
       <c r="E11" s="2">
@@ -3652,13 +3772,13 @@
       <c r="C12" s="2">
         <v>1</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12">
         <v>85391000</v>
       </c>
       <c r="E12" s="2">
         <v>4999950000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12">
         <v>85.391000000000005</v>
       </c>
     </row>
@@ -3672,13 +3792,13 @@
       <c r="C13" s="2">
         <v>2</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13">
         <v>94235000</v>
       </c>
       <c r="E13" s="2">
         <v>4999950000</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13">
         <v>94.234999999999999</v>
       </c>
     </row>
@@ -3692,13 +3812,13 @@
       <c r="C14" s="2">
         <v>3</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14">
         <v>80723000</v>
       </c>
       <c r="E14" s="2">
         <v>4999950000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14">
         <v>80.722999999999999</v>
       </c>
     </row>
@@ -3712,13 +3832,13 @@
       <c r="C15" s="2">
         <v>4</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15">
         <v>80441000</v>
       </c>
       <c r="E15" s="2">
         <v>4999950000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15">
         <v>80.441000000000003</v>
       </c>
     </row>
@@ -3732,13 +3852,13 @@
       <c r="C16" s="2">
         <v>5</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16">
         <v>81582000</v>
       </c>
       <c r="E16" s="2">
         <v>4999950000</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16">
         <v>81.581999999999994</v>
       </c>
     </row>
@@ -3752,13 +3872,13 @@
       <c r="C17" s="2">
         <v>1</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17">
         <v>372495000</v>
       </c>
       <c r="E17" s="2">
         <v>19999900000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17">
         <v>372.495</v>
       </c>
     </row>
@@ -3772,13 +3892,13 @@
       <c r="C18" s="2">
         <v>2</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18">
         <v>356639000</v>
       </c>
       <c r="E18" s="2">
         <v>19999900000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18">
         <v>356.63900000000001</v>
       </c>
     </row>
@@ -3792,13 +3912,13 @@
       <c r="C19" s="2">
         <v>3</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19">
         <v>363973000</v>
       </c>
       <c r="E19" s="2">
         <v>19999900000</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19">
         <v>363.97300000000001</v>
       </c>
     </row>
@@ -3812,13 +3932,13 @@
       <c r="C20" s="2">
         <v>4</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20">
         <v>361800000</v>
       </c>
       <c r="E20" s="2">
         <v>19999900000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20">
         <v>361.8</v>
       </c>
     </row>
@@ -3832,13 +3952,13 @@
       <c r="C21" s="2">
         <v>5</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21">
         <v>362569000</v>
       </c>
       <c r="E21" s="2">
         <v>19999900000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21">
         <v>362.56900000000002</v>
       </c>
     </row>
@@ -3852,7 +3972,7 @@
       <c r="C22" s="2">
         <v>1</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D22" t="s">
         <v>14</v>
       </c>
       <c r="E22" s="2">
@@ -3873,7 +3993,7 @@
       <c r="C23" s="2">
         <v>2</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="D23" t="s">
         <v>14</v>
       </c>
       <c r="E23" s="2">
@@ -3894,7 +4014,7 @@
       <c r="C24" s="2">
         <v>3</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="D24" t="s">
         <v>14</v>
       </c>
       <c r="E24" s="2">
@@ -3915,7 +4035,7 @@
       <c r="C25" s="2">
         <v>4</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="D25" t="s">
         <v>14</v>
       </c>
       <c r="E25" s="2">
@@ -3936,7 +4056,7 @@
       <c r="C26" s="2">
         <v>5</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="D26" t="s">
         <v>15</v>
       </c>
       <c r="E26" s="2">
@@ -3957,7 +4077,7 @@
       <c r="C27" s="2">
         <v>1</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="D27" t="s">
         <v>6</v>
       </c>
       <c r="E27" s="2">
@@ -3978,7 +4098,7 @@
       <c r="C28" s="2">
         <v>2</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="D28" t="s">
         <v>6</v>
       </c>
       <c r="E28" s="2">
@@ -3999,7 +4119,7 @@
       <c r="C29" s="2">
         <v>3</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="D29" t="s">
         <v>6</v>
       </c>
       <c r="E29" s="2">
@@ -4020,7 +4140,7 @@
       <c r="C30" s="2">
         <v>4</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="D30" t="s">
         <v>6</v>
       </c>
       <c r="E30" s="2">
@@ -4041,7 +4161,7 @@
       <c r="C31" s="2">
         <v>5</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="D31" t="s">
         <v>7</v>
       </c>
       <c r="E31" s="2">
@@ -4062,7 +4182,7 @@
       <c r="C32" s="2">
         <v>1</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="D32" t="s">
         <v>16</v>
       </c>
       <c r="E32" s="2">
@@ -4083,7 +4203,7 @@
       <c r="C33" s="2">
         <v>2</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="D33" t="s">
         <v>17</v>
       </c>
       <c r="E33" s="2">
@@ -4104,7 +4224,7 @@
       <c r="C34" s="2">
         <v>3</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="D34" t="s">
         <v>18</v>
       </c>
       <c r="E34" s="2">
@@ -4125,7 +4245,7 @@
       <c r="C35" s="2">
         <v>4</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="D35" t="s">
         <v>17</v>
       </c>
       <c r="E35" s="2">
@@ -4146,7 +4266,7 @@
       <c r="C36" s="2">
         <v>5</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="D36" t="s">
         <v>19</v>
       </c>
       <c r="E36" s="2">
@@ -4167,7 +4287,7 @@
       <c r="C37" s="2">
         <v>1</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="D37" t="s">
         <v>20</v>
       </c>
       <c r="E37" s="2">
@@ -4188,7 +4308,7 @@
       <c r="C38" s="2">
         <v>2</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="D38" t="s">
         <v>21</v>
       </c>
       <c r="E38" s="2">
@@ -4209,7 +4329,7 @@
       <c r="C39" s="2">
         <v>3</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="D39" t="s">
         <v>22</v>
       </c>
       <c r="E39" s="2">
@@ -4230,7 +4350,7 @@
       <c r="C40" s="2">
         <v>4</v>
       </c>
-      <c r="D40" s="3" t="s">
+      <c r="D40" t="s">
         <v>23</v>
       </c>
       <c r="E40" s="2">
@@ -4251,7 +4371,7 @@
       <c r="C41" s="2">
         <v>5</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="D41" t="s">
         <v>24</v>
       </c>
       <c r="E41" s="2">
@@ -4260,6 +4380,211 @@
       <c r="F41">
         <f t="shared" si="0"/>
         <v>0.14199999999999999</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>5</v>
+      </c>
+      <c r="B42">
+        <v>500000</v>
+      </c>
+      <c r="C42" s="2">
+        <v>1</v>
+      </c>
+      <c r="D42" s="11">
+        <v>2108176000</v>
+      </c>
+      <c r="E42" s="2">
+        <v>124999750000</v>
+      </c>
+      <c r="F42" s="2">
+        <v>2108.1759999999999</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>5</v>
+      </c>
+      <c r="B43">
+        <v>500000</v>
+      </c>
+      <c r="C43" s="2">
+        <v>2</v>
+      </c>
+      <c r="D43" s="11">
+        <v>2075004000</v>
+      </c>
+      <c r="E43" s="2">
+        <v>124999750000</v>
+      </c>
+      <c r="F43" s="2">
+        <v>2075.0039999999999</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>5</v>
+      </c>
+      <c r="B44">
+        <v>500000</v>
+      </c>
+      <c r="C44" s="2">
+        <v>3</v>
+      </c>
+      <c r="D44" s="11">
+        <v>2088027000</v>
+      </c>
+      <c r="E44" s="2">
+        <v>124999750000</v>
+      </c>
+      <c r="F44" s="2">
+        <v>2088.027</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>5</v>
+      </c>
+      <c r="B45">
+        <v>500000</v>
+      </c>
+      <c r="C45" s="2">
+        <v>4</v>
+      </c>
+      <c r="D45" s="11">
+        <v>2192899000</v>
+      </c>
+      <c r="E45" s="2">
+        <v>124999750000</v>
+      </c>
+      <c r="F45" s="2">
+        <v>2192.8989999999999</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>5</v>
+      </c>
+      <c r="B46">
+        <v>500000</v>
+      </c>
+      <c r="C46" s="2">
+        <v>5</v>
+      </c>
+      <c r="D46" s="11">
+        <v>2205847000</v>
+      </c>
+      <c r="E46" s="2">
+        <v>124999750000</v>
+      </c>
+      <c r="F46" s="2">
+        <v>2205.8470000000002</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>13</v>
+      </c>
+      <c r="B47">
+        <v>500000</v>
+      </c>
+      <c r="C47" s="2">
+        <v>1</v>
+      </c>
+      <c r="D47" t="s">
+        <v>36</v>
+      </c>
+      <c r="E47" s="2">
+        <v>8813340</v>
+      </c>
+      <c r="F47" s="2">
+        <f>VALUE(SUBSTITUTE(D47,".",","))</f>
+        <v>0.48799999999999999</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>13</v>
+      </c>
+      <c r="B48">
+        <v>500000</v>
+      </c>
+      <c r="C48" s="2">
+        <v>2</v>
+      </c>
+      <c r="D48" t="s">
+        <v>37</v>
+      </c>
+      <c r="E48" s="2">
+        <v>8812792</v>
+      </c>
+      <c r="F48" s="2">
+        <f>VALUE(SUBSTITUTE(D48,".",","))</f>
+        <v>0.496</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>13</v>
+      </c>
+      <c r="B49">
+        <v>500000</v>
+      </c>
+      <c r="C49" s="2">
+        <v>3</v>
+      </c>
+      <c r="D49" t="s">
+        <v>36</v>
+      </c>
+      <c r="E49" s="2">
+        <v>8813013</v>
+      </c>
+      <c r="F49" s="2">
+        <f>VALUE(SUBSTITUTE(D49,".",","))</f>
+        <v>0.48799999999999999</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>13</v>
+      </c>
+      <c r="B50">
+        <v>500000</v>
+      </c>
+      <c r="C50" s="2">
+        <v>4</v>
+      </c>
+      <c r="D50" t="s">
+        <v>38</v>
+      </c>
+      <c r="E50" s="2">
+        <v>8812595</v>
+      </c>
+      <c r="F50" s="2">
+        <f>VALUE(SUBSTITUTE(D50,".",","))</f>
+        <v>0.41099999999999998</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>13</v>
+      </c>
+      <c r="B51">
+        <v>500000</v>
+      </c>
+      <c r="C51" s="2">
+        <v>5</v>
+      </c>
+      <c r="D51" t="s">
+        <v>39</v>
+      </c>
+      <c r="E51" s="2">
+        <v>8812905</v>
+      </c>
+      <c r="F51" s="2">
+        <f>VALUE(SUBSTITUTE(D51,".",","))</f>
+        <v>0.39700000000000002</v>
       </c>
     </row>
   </sheetData>
@@ -4273,10 +4598,10 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="18.140625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="22.5703125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="19.140625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18.140625" customWidth="1"/>
+    <col min="4" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="19.140625" customWidth="1"/>
     <col min="8" max="8" width="9.7109375" customWidth="1"/>
     <col min="9" max="9" width="27" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="23.85546875" bestFit="1" customWidth="1"/>
@@ -4287,104 +4612,125 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="5">
+      <c r="A2" s="4">
         <v>1000</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="3">
         <f>AVERAGE(dados_brutos!F2:F6)</f>
         <v>5.6000000000000008E-3</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="3">
         <f>_xlfn.STDEV.S(dados_brutos!F2:F6)</f>
         <v>5.4772255750516611E-4</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="3">
         <f>AVERAGE(dados_brutos!F22:F26)</f>
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="3">
         <f>_xlfn.STDEV.S(dados_brutos!F22:F26)</f>
         <v>4.4721359549995795E-4</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="5">
+      <c r="A3" s="4">
         <v>10000</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="3">
         <f>AVERAGE(dados_brutos!F7:F11)</f>
         <v>0.57619999999999993</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="3">
         <f>_xlfn.STDEV.S(dados_brutos!F7:F11)</f>
         <v>1.3608820668963212E-2</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="3">
         <f>AVERAGE(dados_brutos!F27:F31)</f>
         <v>5.8000000000000005E-3</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="3">
         <f>_xlfn.STDEV.S(dados_brutos!F27:F31)</f>
         <v>4.4721359549995795E-4</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5">
+      <c r="A4" s="4">
         <v>100000</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="3">
         <f>AVERAGE(dados_brutos!F12:F16)</f>
         <v>84.474399999999989</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="3">
         <f>_xlfn.STDEV.S(dados_brutos!F12:F16)</f>
         <v>5.8055310523672174</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="3">
         <f>AVERAGE(dados_brutos!F32:F36)</f>
         <v>6.5600000000000006E-2</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="3">
         <f>_xlfn.STDEV.S(dados_brutos!F32:F36)</f>
         <v>4.9799598391954908E-3</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5">
+      <c r="A5" s="4">
         <v>200000</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="3">
         <f>AVERAGE(dados_brutos!F17:F21)</f>
         <v>363.49519999999995</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="3">
         <f>_xlfn.STDEV.S(dados_brutos!F17:F21)</f>
         <v>5.7437731675267241</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="3">
         <f>AVERAGE(dados_brutos!F37:F41)</f>
         <v>0.14499999999999999</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="3">
         <f>_xlfn.STDEV.S(dados_brutos!F37:F41)</f>
         <v>2.9154759474226528E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
+        <v>500000</v>
+      </c>
+      <c r="B6" s="3">
+        <f>AVERAGE(dados_brutos!F42:F46)</f>
+        <v>2133.9906000000001</v>
+      </c>
+      <c r="C6" s="3">
+        <f>_xlfn.STDEV.S(dados_brutos!F42:F46)</f>
+        <v>61.016405353806341</v>
+      </c>
+      <c r="D6" s="3">
+        <f>AVERAGE(dados_brutos!F47:F51)</f>
+        <v>0.45600000000000007</v>
+      </c>
+      <c r="E6" s="3">
+        <f>_xlfn.STDEV.S(dados_brutos!F47:F51)</f>
+        <v>4.7838269199459965E-2</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -4393,24 +4739,24 @@
       <c r="D15" s="1"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -4424,7 +4770,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40ECAFDB-836C-4B3E-854B-6F93334FE479}">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.28515625" customWidth="1"/>
@@ -4575,61 +4921,103 @@
         <v>3521928.0948873623</v>
       </c>
     </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>500000</v>
+      </c>
+      <c r="B6" s="2">
+        <f>AVERAGE(dados_brutos!E42:E46)</f>
+        <v>124999750000</v>
+      </c>
+      <c r="C6">
+        <f>_xlfn.STDEV.S(dados_brutos!E42:E46)</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="12">
+        <f>'Tabela 1'!A6^2</f>
+        <v>250000000000</v>
+      </c>
+      <c r="E6" s="2">
+        <f>AVERAGE(dados_brutos!E47:E51)</f>
+        <v>8812929</v>
+      </c>
+      <c r="F6">
+        <f>_xlfn.STDEV.S(dados_brutos!E47:E51)</f>
+        <v>276.98285145474262</v>
+      </c>
+      <c r="G6">
+        <f>'Tabela 1'!A6*(LOG('Tabela 1'!A6,2))</f>
+        <v>9465784.2846620865</v>
+      </c>
+    </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F14" s="7"/>
+      <c r="C14" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="8">
+      <c r="B15" s="9">
         <v>1000</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="14">
         <v>499500</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="14">
         <v>8694.6</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="8">
+      <c r="B16" s="9">
         <v>10000</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="14">
         <v>49995000</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="14">
         <v>120281.8</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B17" s="8">
+      <c r="B17" s="9">
         <v>100000</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="14">
         <v>4999950000</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="14">
         <v>1532760.2</v>
       </c>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B18" s="8">
+      <c r="B18" s="9">
         <v>200000</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="14">
         <v>19999900000</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="14">
         <v>3264479</v>
       </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B19" s="10">
+        <v>500000</v>
+      </c>
+      <c r="C19" s="13">
+        <v>124999750000</v>
+      </c>
+      <c r="D19" s="13">
+        <v>8812929</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D32" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
